--- a/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
+++ b/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COM\Desktop\automation\Korean_oriented_pharmacy_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EEAD812-34ED-42C4-BD80-F3EF60DC8F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF4C620-8E67-412B-83A7-97ABDCEB80E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="4110" windowWidth="21570" windowHeight="11385" xr2:uid="{C0D19388-C7FF-48FF-BA24-2743E4CC240C}"/>
+    <workbookView xWindow="2640" yWindow="3495" windowWidth="21570" windowHeight="11385" xr2:uid="{7063B7E8-49C7-46DE-8DFF-9032279CD1EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>주문자</t>
   </si>
@@ -106,6 +106,21 @@
   </si>
   <si>
     <t>녹용대보탕</t>
+  </si>
+  <si>
+    <t>옹기한약국</t>
+  </si>
+  <si>
+    <t>테스트</t>
+  </si>
+  <si>
+    <t>전북특별자치도 익산시 무왕로 878 (신동) 옹기한약국</t>
+  </si>
+  <si>
+    <t>010-1234-5678</t>
+  </si>
+  <si>
+    <t>쌍화탕/국산숙지황사용(가미)</t>
   </si>
 </sst>
 </file>
@@ -507,8 +522,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1E5AF8-A4DA-4D8E-BB21-F4C20C6E3623}">
-  <dimension ref="A1:M2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AAB517-E9DB-4663-B2E3-0F9342E6A05C}">
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
@@ -518,10 +533,10 @@
     <col min="5" max="5" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="89" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="9" style="1"/>
-    <col min="13" max="13" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.75" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -604,6 +619,45 @@
       </c>
       <c r="M2" s="5" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="6">
+        <v>54645</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
+++ b/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COM\Desktop\automation\Korean_oriented_pharmacy_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF4C620-8E67-412B-83A7-97ABDCEB80E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C80397FC-F5C6-4302-9846-D034EC1DCCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="3495" windowWidth="21570" windowHeight="11385" xr2:uid="{7063B7E8-49C7-46DE-8DFF-9032279CD1EC}"/>
+    <workbookView xWindow="1860" yWindow="1110" windowWidth="21570" windowHeight="11385" xr2:uid="{BD090D00-EFB2-4278-A21A-60F0C5CE51F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>주문자</t>
   </si>
@@ -75,49 +75,25 @@
     <t>처방명</t>
   </si>
   <si>
-    <t>해미소한의원</t>
-  </si>
-  <si>
-    <t>경기 의왕시 포일로 43 (내손동, 대림프라자) 302호</t>
-  </si>
-  <si>
-    <t>031-424-2110</t>
-  </si>
-  <si>
-    <t>양승후</t>
-  </si>
-  <si>
-    <t>인천광역시 연수구 송도과학로 85 연세대학교 국제캠퍼스 송도학사 A동 859호(1층 택배보관실)</t>
-  </si>
-  <si>
-    <t>01033523910</t>
-  </si>
-  <si>
-    <t>010-3323-3910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">택배/  </t>
+    <t>옹기한약국</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>테스트</t>
+  </si>
+  <si>
+    <t>전북특별자치도 익산시 무왕로 878 (신동) 옹기한약국</t>
+  </si>
+  <si>
+    <t>010-1234-5678</t>
+  </si>
+  <si>
+    <t>택배/  로젠 44265351104</t>
+  </si>
+  <si>
     <t>택배</t>
-  </si>
-  <si>
-    <t>녹용대보탕</t>
-  </si>
-  <si>
-    <t>옹기한약국</t>
-  </si>
-  <si>
-    <t>테스트</t>
-  </si>
-  <si>
-    <t>전북특별자치도 익산시 무왕로 878 (신동) 옹기한약국</t>
-  </si>
-  <si>
-    <t>010-1234-5678</t>
   </si>
   <si>
     <t>쌍화탕/국산숙지황사용(가미)</t>
@@ -522,20 +498,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55AAB517-E9DB-4663-B2E3-0F9342E6A05C}">
-  <dimension ref="A1:M3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF7BA17-CFCD-4E89-B69A-FFEAE1BA84A6}">
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="89" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="50.375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="9" style="1"/>
+    <col min="10" max="10" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9" style="1"/>
     <col min="13" max="13" width="27.75" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -543,7 +520,7 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -584,80 +561,41 @@
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6">
-        <v>16022</v>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="6">
+        <v>54645</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="6">
-        <v>21983</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="6">
-        <v>54645</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
+++ b/Korean_oriented_pharmacy_automation/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COM\Desktop\automation\Korean_oriented_pharmacy_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C80397FC-F5C6-4302-9846-D034EC1DCCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D28C247-E7F1-4F44-8048-A2617CA1856E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1110" windowWidth="21570" windowHeight="11385" xr2:uid="{BD090D00-EFB2-4278-A21A-60F0C5CE51F4}"/>
+    <workbookView xWindow="6165" yWindow="1875" windowWidth="21570" windowHeight="12735" xr2:uid="{4CD27E10-7EEA-42B0-A49D-D52E291CC699}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>주문자</t>
   </si>
@@ -75,28 +75,49 @@
     <t>처방명</t>
   </si>
   <si>
+    <t>해미소한의원</t>
+  </si>
+  <si>
+    <t>경기 의왕시 포일로 43 (내손동, 대림프라자) 302호</t>
+  </si>
+  <si>
+    <t>031-424-2110</t>
+  </si>
+  <si>
+    <t>김영숙</t>
+  </si>
+  <si>
+    <t>경기도 의왕시 내손중앙로 11 1104동 1702호  이편한세상 인덕원 더 퍼스트 1단지</t>
+  </si>
+  <si>
+    <t>01052069226</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">택배/  </t>
+  </si>
+  <si>
+    <t>택배</t>
+  </si>
+  <si>
+    <t>개별처방(가감)(가미)</t>
+  </si>
+  <si>
     <t>옹기한약국</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>테스트</t>
-  </si>
-  <si>
-    <t>전북특별자치도 익산시 무왕로 878 (신동) 옹기한약국</t>
-  </si>
-  <si>
-    <t>010-1234-5678</t>
-  </si>
-  <si>
-    <t>택배/  로젠 44265351104</t>
-  </si>
-  <si>
-    <t>택배</t>
-  </si>
-  <si>
-    <t>쌍화탕/국산숙지황사용(가미)</t>
+    <t>ㄹㅇㄴㄹㅇㄴㄹㅇㄴㄹㄴㅇ</t>
+  </si>
+  <si>
+    <t>010-5955-8893</t>
+  </si>
+  <si>
+    <t>택배/  로젠 44298256052</t>
+  </si>
+  <si>
+    <t>가감갈근해기탕</t>
   </si>
 </sst>
 </file>
@@ -498,29 +519,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF7BA17-CFCD-4E89-B69A-FFEAE1BA84A6}">
-  <dimension ref="A1:M2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B6DE25-3A2A-47E0-B706-28FA202782FB}">
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="50.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="76.5" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="1"/>
-    <col min="13" max="13" width="27.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -561,41 +582,78 @@
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>14</v>
+      <c r="B2" s="6">
+        <v>16022</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="6">
-        <v>54645</v>
+        <v>16021</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>20</v>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
